--- a/pfmea_merger/templates/PFMEA_SBM_SOREN_Template.xlsx
+++ b/pfmea_merger/templates/PFMEA_SBM_SOREN_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sargoli.h\Documents\GitHub\Excel_APQP\pfmea_merger\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2A9A31-1482-42B7-8C0D-9609A36ABF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33F885D-2127-4EAA-BC82-1FF3282CF5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2848,7 +2848,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="291">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3629,27 +3629,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="63" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="58" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="64">
     <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3717,7 +3696,14 @@
     <cellStyle name="Normal_FMEA" xfId="63" xr:uid="{41089CB8-11F0-4EBD-B8F4-A5798F568795}"/>
     <cellStyle name="Normal_Sheet1" xfId="62" xr:uid="{6919F245-F011-4C3D-A39F-07F7C4A22EE0}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4508,11 +4494,10 @@
     <col min="22" max="22" width="11.85546875" style="23" customWidth="1"/>
     <col min="23" max="25" width="9.140625" style="1"/>
     <col min="26" max="26" width="13.5703125" style="1" customWidth="1"/>
-    <col min="27" max="43" width="9.140625" style="1"/>
-    <col min="44" max="16384" width="9.140625" style="290"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="276" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="185" t="s">
         <v>136</v>
       </c>
@@ -4559,15 +4544,11 @@
       <c r="AJ1" s="162"/>
       <c r="AK1" s="162"/>
       <c r="AL1" s="163"/>
-      <c r="AM1" s="69"/>
-      <c r="AN1" s="69"/>
-      <c r="AO1" s="69"/>
-      <c r="AP1" s="69"/>
       <c r="AQ1" s="88" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="276" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" s="69" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="188"/>
       <c r="B2" s="189"/>
       <c r="C2" s="189"/>
@@ -4608,16 +4589,12 @@
       <c r="AJ2" s="165"/>
       <c r="AK2" s="165"/>
       <c r="AL2" s="166"/>
-      <c r="AM2" s="69"/>
-      <c r="AN2" s="69"/>
-      <c r="AO2" s="69"/>
-      <c r="AP2" s="69"/>
       <c r="AQ2" s="88" cm="1">
-        <f t="array" ref="AQ2">INDEX(_xlfn._xlws.SORT($M$10:$M901,1,-1),COUNT(_xlfn._xlws.SORT($M$10:$M901,1,-1))*0.2)</f>
+        <f t="array" ref="AQ2">INDEX(_xlfn._xlws.SORT($M$9:$M901,1,-1),COUNT(_xlfn._xlws.SORT($M$9:$M901,1,-1))*0.2)</f>
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:43" s="276" customFormat="1" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" s="69" customFormat="1" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="191"/>
       <c r="B3" s="192"/>
       <c r="C3" s="192"/>
@@ -4660,13 +4637,8 @@
       <c r="AJ3" s="165"/>
       <c r="AK3" s="165"/>
       <c r="AL3" s="166"/>
-      <c r="AM3" s="69"/>
-      <c r="AN3" s="69"/>
-      <c r="AO3" s="69"/>
-      <c r="AP3" s="69"/>
-      <c r="AQ3" s="69"/>
-    </row>
-    <row r="4" spans="1:43" s="277" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:43" s="70" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="203" t="s">
         <v>166</v>
       </c>
@@ -4715,13 +4687,8 @@
       <c r="AJ4" s="165"/>
       <c r="AK4" s="165"/>
       <c r="AL4" s="166"/>
-      <c r="AM4" s="70"/>
-      <c r="AN4" s="70"/>
-      <c r="AO4" s="70"/>
-      <c r="AP4" s="70"/>
-      <c r="AQ4" s="70"/>
-    </row>
-    <row r="5" spans="1:43" s="277" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:43" s="70" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="176" t="s">
         <v>140</v>
       </c>
@@ -4768,13 +4735,8 @@
       <c r="AJ5" s="165"/>
       <c r="AK5" s="165"/>
       <c r="AL5" s="166"/>
-      <c r="AM5" s="70"/>
-      <c r="AN5" s="70"/>
-      <c r="AO5" s="70"/>
-      <c r="AP5" s="70"/>
-      <c r="AQ5" s="70"/>
-    </row>
-    <row r="6" spans="1:43" s="277" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:43" s="70" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="183" t="s">
         <v>143</v>
       </c>
@@ -4821,13 +4783,8 @@
       <c r="AJ6" s="168"/>
       <c r="AK6" s="168"/>
       <c r="AL6" s="169"/>
-      <c r="AM6" s="70"/>
-      <c r="AN6" s="70"/>
-      <c r="AO6" s="70"/>
-      <c r="AP6" s="70"/>
-      <c r="AQ6" s="70"/>
-    </row>
-    <row r="7" spans="1:43" s="278" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="217" t="s">
         <v>2</v>
       </c>
@@ -4934,13 +4891,8 @@
       <c r="AL7" s="252" t="s">
         <v>304</v>
       </c>
-      <c r="AM7" s="2"/>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2"/>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2"/>
-    </row>
-    <row r="8" spans="1:43" s="278" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="218"/>
       <c r="B8" s="224"/>
       <c r="C8" s="224"/>
@@ -4991,13 +4943,8 @@
       <c r="AJ8" s="251"/>
       <c r="AK8" s="251"/>
       <c r="AL8" s="253"/>
-      <c r="AM8" s="2"/>
-      <c r="AN8" s="2"/>
-      <c r="AO8" s="2"/>
-      <c r="AP8" s="2"/>
-      <c r="AQ8" s="2"/>
-    </row>
-    <row r="9" spans="1:43" s="279" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:43" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="137" t="s">
         <v>67</v>
       </c>
@@ -5048,7 +4995,7 @@
       <c r="AP9" s="7"/>
       <c r="AQ9" s="7"/>
     </row>
-    <row r="10" spans="1:43" s="279" customFormat="1" ht="300" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" s="5" customFormat="1" ht="300" x14ac:dyDescent="0.25">
       <c r="A10" s="222" t="s">
         <v>53</v>
       </c>
@@ -5136,13 +5083,8 @@
       <c r="AJ10" s="109"/>
       <c r="AK10" s="109"/>
       <c r="AL10" s="110"/>
-      <c r="AM10" s="5"/>
-      <c r="AN10" s="5"/>
-      <c r="AO10" s="5"/>
-      <c r="AP10" s="5"/>
-      <c r="AQ10" s="5"/>
-    </row>
-    <row r="11" spans="1:43" s="280" customFormat="1" ht="281.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:43" s="67" customFormat="1" ht="281.25" x14ac:dyDescent="0.25">
       <c r="A11" s="222"/>
       <c r="B11" s="216"/>
       <c r="C11" s="12" t="s">
@@ -5212,7 +5154,7 @@
       <c r="AP11" s="5"/>
       <c r="AQ11" s="5"/>
     </row>
-    <row r="12" spans="1:43" s="281" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" s="3" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="139" t="s">
         <v>25</v>
       </c>
@@ -5286,7 +5228,7 @@
       <c r="AP12" s="67"/>
       <c r="AQ12" s="67"/>
     </row>
-    <row r="13" spans="1:43" s="281" customFormat="1" ht="208.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" s="3" customFormat="1" ht="208.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="219" t="s">
         <v>24</v>
       </c>
@@ -5374,13 +5316,8 @@
       <c r="AJ13" s="111"/>
       <c r="AK13" s="111"/>
       <c r="AL13" s="112"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="3"/>
-      <c r="AQ13" s="3"/>
-    </row>
-    <row r="14" spans="1:43" s="281" customFormat="1" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:43" s="3" customFormat="1" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="219"/>
       <c r="B14" s="216"/>
       <c r="C14" s="12" t="s">
@@ -5464,13 +5401,8 @@
       <c r="AJ14" s="111"/>
       <c r="AK14" s="111"/>
       <c r="AL14" s="112"/>
-      <c r="AM14" s="3"/>
-      <c r="AN14" s="3"/>
-      <c r="AO14" s="3"/>
-      <c r="AP14" s="3"/>
-      <c r="AQ14" s="3"/>
-    </row>
-    <row r="15" spans="1:43" s="281" customFormat="1" ht="189.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:43" s="3" customFormat="1" ht="189.75" x14ac:dyDescent="0.25">
       <c r="A15" s="219"/>
       <c r="B15" s="216"/>
       <c r="C15" s="29" t="s">
@@ -5554,13 +5486,8 @@
       <c r="AJ15" s="111"/>
       <c r="AK15" s="111"/>
       <c r="AL15" s="112"/>
-      <c r="AM15" s="3"/>
-      <c r="AN15" s="3"/>
-      <c r="AO15" s="3"/>
-      <c r="AP15" s="3"/>
-      <c r="AQ15" s="3"/>
-    </row>
-    <row r="16" spans="1:43" s="281" customFormat="1" ht="133.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:43" s="3" customFormat="1" ht="133.5" x14ac:dyDescent="0.25">
       <c r="A16" s="219"/>
       <c r="B16" s="216"/>
       <c r="C16" s="12" t="s">
@@ -5644,13 +5571,8 @@
       <c r="AJ16" s="111"/>
       <c r="AK16" s="111"/>
       <c r="AL16" s="112"/>
-      <c r="AM16" s="3"/>
-      <c r="AN16" s="3"/>
-      <c r="AO16" s="3"/>
-      <c r="AP16" s="3"/>
-      <c r="AQ16" s="3"/>
-    </row>
-    <row r="17" spans="1:43" s="281" customFormat="1" ht="133.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:43" s="3" customFormat="1" ht="133.5" x14ac:dyDescent="0.25">
       <c r="A17" s="219"/>
       <c r="B17" s="216"/>
       <c r="C17" s="12" t="s">
@@ -5732,13 +5654,8 @@
       <c r="AJ17" s="111"/>
       <c r="AK17" s="111"/>
       <c r="AL17" s="112"/>
-      <c r="AM17" s="3"/>
-      <c r="AN17" s="3"/>
-      <c r="AO17" s="3"/>
-      <c r="AP17" s="3"/>
-      <c r="AQ17" s="3"/>
-    </row>
-    <row r="18" spans="1:43" s="281" customFormat="1" ht="133.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:43" s="3" customFormat="1" ht="133.5" x14ac:dyDescent="0.25">
       <c r="A18" s="219"/>
       <c r="B18" s="216"/>
       <c r="C18" s="12" t="s">
@@ -5802,13 +5719,8 @@
       <c r="AJ18" s="111"/>
       <c r="AK18" s="111"/>
       <c r="AL18" s="112"/>
-      <c r="AM18" s="3"/>
-      <c r="AN18" s="3"/>
-      <c r="AO18" s="3"/>
-      <c r="AP18" s="3"/>
-      <c r="AQ18" s="3"/>
-    </row>
-    <row r="19" spans="1:43" s="281" customFormat="1" ht="131.25" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:43" s="3" customFormat="1" ht="131.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="219"/>
       <c r="B19" s="216"/>
       <c r="C19" s="12" t="s">
@@ -5874,29 +5786,8 @@
         <f>S19*R19</f>
         <v>21</v>
       </c>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="3"/>
-      <c r="AF19" s="3"/>
-      <c r="AG19" s="3"/>
-      <c r="AH19" s="3"/>
-      <c r="AI19" s="3"/>
-      <c r="AJ19" s="3"/>
-      <c r="AK19" s="3"/>
-      <c r="AL19" s="3"/>
-      <c r="AM19" s="3"/>
-      <c r="AN19" s="3"/>
-      <c r="AO19" s="3"/>
-      <c r="AP19" s="3"/>
-      <c r="AQ19" s="3"/>
-    </row>
-    <row r="20" spans="1:43" s="281" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:43" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="219"/>
       <c r="B20" s="216"/>
       <c r="C20" s="225" t="s">
@@ -5960,13 +5851,8 @@
       <c r="AJ20" s="111"/>
       <c r="AK20" s="111"/>
       <c r="AL20" s="112"/>
-      <c r="AM20" s="3"/>
-      <c r="AN20" s="3"/>
-      <c r="AO20" s="3"/>
-      <c r="AP20" s="3"/>
-      <c r="AQ20" s="3"/>
-    </row>
-    <row r="21" spans="1:43" s="282" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:43" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="219"/>
       <c r="B21" s="216"/>
       <c r="C21" s="225"/>
@@ -6034,7 +5920,7 @@
       <c r="AP21" s="3"/>
       <c r="AQ21" s="3"/>
     </row>
-    <row r="22" spans="1:43" s="282" customFormat="1" ht="300" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" customFormat="1" ht="300" x14ac:dyDescent="0.25">
       <c r="A22" s="212" t="s">
         <v>28</v>
       </c>
@@ -6122,13 +6008,8 @@
       <c r="AJ22" s="111"/>
       <c r="AK22" s="111"/>
       <c r="AL22" s="112"/>
-      <c r="AM22"/>
-      <c r="AN22"/>
-      <c r="AO22"/>
-      <c r="AP22"/>
-      <c r="AQ22"/>
-    </row>
-    <row r="23" spans="1:43" s="283" customFormat="1" ht="243.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:43" s="31" customFormat="1" ht="243.75" x14ac:dyDescent="0.25">
       <c r="A23" s="212"/>
       <c r="B23" s="214"/>
       <c r="C23" s="58" t="s">
@@ -6218,7 +6099,7 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="283" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" s="31" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A24" s="212"/>
       <c r="B24" s="214"/>
       <c r="C24" s="121" t="s">
@@ -6302,13 +6183,8 @@
       <c r="AJ24" s="111"/>
       <c r="AK24" s="111"/>
       <c r="AL24" s="112"/>
-      <c r="AM24" s="31"/>
-      <c r="AN24" s="31"/>
-      <c r="AO24" s="31"/>
-      <c r="AP24" s="31"/>
-      <c r="AQ24" s="31"/>
-    </row>
-    <row r="25" spans="1:43" s="283" customFormat="1" ht="225" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:43" s="31" customFormat="1" ht="225" x14ac:dyDescent="0.25">
       <c r="A25" s="212"/>
       <c r="B25" s="214"/>
       <c r="C25" s="66" t="s">
@@ -6392,13 +6268,8 @@
       <c r="AJ25" s="111"/>
       <c r="AK25" s="111"/>
       <c r="AL25" s="112"/>
-      <c r="AM25" s="31"/>
-      <c r="AN25" s="31"/>
-      <c r="AO25" s="31"/>
-      <c r="AP25" s="31"/>
-      <c r="AQ25" s="31"/>
-    </row>
-    <row r="26" spans="1:43" s="282" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:43" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A26" s="212"/>
       <c r="B26" s="214"/>
       <c r="C26" s="48" t="s">
@@ -6488,7 +6359,7 @@
       <c r="AP26" s="31"/>
       <c r="AQ26" s="31"/>
     </row>
-    <row r="27" spans="1:43" s="282" customFormat="1" ht="187.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" customFormat="1" ht="187.5" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="214"/>
       <c r="C27" s="48" t="s">
@@ -6552,13 +6423,8 @@
       <c r="AJ27" s="111"/>
       <c r="AK27" s="111"/>
       <c r="AL27" s="112"/>
-      <c r="AM27"/>
-      <c r="AN27"/>
-      <c r="AO27"/>
-      <c r="AP27"/>
-      <c r="AQ27"/>
-    </row>
-    <row r="28" spans="1:43" s="282" customFormat="1" ht="206.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:43" customFormat="1" ht="206.25" x14ac:dyDescent="0.25">
       <c r="A28" s="212"/>
       <c r="B28" s="214"/>
       <c r="C28" s="48" t="s">
@@ -6622,13 +6488,8 @@
       <c r="AJ28" s="111"/>
       <c r="AK28" s="111"/>
       <c r="AL28" s="112"/>
-      <c r="AM28"/>
-      <c r="AN28"/>
-      <c r="AO28"/>
-      <c r="AP28"/>
-      <c r="AQ28"/>
-    </row>
-    <row r="29" spans="1:43" s="282" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:43" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="212"/>
       <c r="B29" s="214"/>
       <c r="C29" s="48" t="s">
@@ -6712,13 +6573,8 @@
       <c r="AJ29" s="111"/>
       <c r="AK29" s="111"/>
       <c r="AL29" s="112"/>
-      <c r="AM29"/>
-      <c r="AN29"/>
-      <c r="AO29"/>
-      <c r="AP29"/>
-      <c r="AQ29"/>
-    </row>
-    <row r="30" spans="1:43" s="282" customFormat="1" ht="187.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:43" customFormat="1" ht="187.5" x14ac:dyDescent="0.25">
       <c r="A30" s="212"/>
       <c r="B30" s="214"/>
       <c r="C30" s="48" t="s">
@@ -6802,13 +6658,8 @@
       <c r="AJ30" s="111"/>
       <c r="AK30" s="111"/>
       <c r="AL30" s="112"/>
-      <c r="AM30"/>
-      <c r="AN30"/>
-      <c r="AO30"/>
-      <c r="AP30"/>
-      <c r="AQ30"/>
-    </row>
-    <row r="31" spans="1:43" s="282" customFormat="1" ht="112.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:43" customFormat="1" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A31" s="212"/>
       <c r="B31" s="214"/>
       <c r="C31" s="215" t="s">
@@ -6872,13 +6723,8 @@
       <c r="AJ31" s="111"/>
       <c r="AK31" s="111"/>
       <c r="AL31" s="112"/>
-      <c r="AM31"/>
-      <c r="AN31"/>
-      <c r="AO31"/>
-      <c r="AP31"/>
-      <c r="AQ31"/>
-    </row>
-    <row r="32" spans="1:43" s="284" customFormat="1" ht="194.45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:43" s="4" customFormat="1" ht="194.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="212"/>
       <c r="B32" s="214"/>
       <c r="C32" s="215"/>
@@ -6946,7 +6792,7 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="284" customFormat="1" ht="302.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" s="4" customFormat="1" ht="302.25" x14ac:dyDescent="0.25">
       <c r="A33" s="222" t="s">
         <v>29</v>
       </c>
@@ -7014,13 +6860,8 @@
       <c r="AJ33" s="111"/>
       <c r="AK33" s="111"/>
       <c r="AL33" s="112"/>
-      <c r="AM33" s="4"/>
-      <c r="AN33" s="4"/>
-      <c r="AO33" s="4"/>
-      <c r="AP33" s="4"/>
-      <c r="AQ33" s="4"/>
-    </row>
-    <row r="34" spans="1:43" s="284" customFormat="1" ht="228" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:43" s="4" customFormat="1" ht="228" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="222"/>
       <c r="B34" s="216"/>
       <c r="C34" s="225"/>
@@ -7080,13 +6921,8 @@
       <c r="AJ34" s="111"/>
       <c r="AK34" s="111"/>
       <c r="AL34" s="112"/>
-      <c r="AM34" s="4"/>
-      <c r="AN34" s="4"/>
-      <c r="AO34" s="4"/>
-      <c r="AP34" s="4"/>
-      <c r="AQ34" s="4"/>
-    </row>
-    <row r="35" spans="1:43" s="284" customFormat="1" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:43" s="4" customFormat="1" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="222"/>
       <c r="B35" s="216"/>
       <c r="C35" s="225"/>
@@ -7146,13 +6982,8 @@
       <c r="AJ35" s="111"/>
       <c r="AK35" s="111"/>
       <c r="AL35" s="112"/>
-      <c r="AM35" s="4"/>
-      <c r="AN35" s="4"/>
-      <c r="AO35" s="4"/>
-      <c r="AP35" s="4"/>
-      <c r="AQ35" s="4"/>
-    </row>
-    <row r="36" spans="1:43" s="284" customFormat="1" ht="393.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:43" s="4" customFormat="1" ht="393.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="222"/>
       <c r="B36" s="216"/>
       <c r="C36" s="12" t="s">
@@ -7216,13 +7047,8 @@
       <c r="AJ36" s="111"/>
       <c r="AK36" s="111"/>
       <c r="AL36" s="112"/>
-      <c r="AM36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="AO36" s="4"/>
-      <c r="AP36" s="4"/>
-      <c r="AQ36" s="4"/>
-    </row>
-    <row r="37" spans="1:43" s="284" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:43" s="4" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="222"/>
       <c r="B37" s="216"/>
       <c r="C37" s="12" t="s">
@@ -7286,13 +7112,8 @@
       <c r="AJ37" s="111"/>
       <c r="AK37" s="111"/>
       <c r="AL37" s="112"/>
-      <c r="AM37" s="4"/>
-      <c r="AN37" s="4"/>
-      <c r="AO37" s="4"/>
-      <c r="AP37" s="4"/>
-      <c r="AQ37" s="4"/>
-    </row>
-    <row r="38" spans="1:43" s="284" customFormat="1" ht="295.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:43" s="4" customFormat="1" ht="295.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="222"/>
       <c r="B38" s="216"/>
       <c r="C38" s="48" t="s">
@@ -7356,13 +7177,8 @@
       <c r="AJ38" s="111"/>
       <c r="AK38" s="111"/>
       <c r="AL38" s="112"/>
-      <c r="AM38" s="4"/>
-      <c r="AN38" s="4"/>
-      <c r="AO38" s="4"/>
-      <c r="AP38" s="4"/>
-      <c r="AQ38" s="4"/>
-    </row>
-    <row r="39" spans="1:43" s="284" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:43" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="222"/>
       <c r="B39" s="216"/>
       <c r="C39" s="215" t="s">
@@ -7426,13 +7242,8 @@
       <c r="AJ39" s="111"/>
       <c r="AK39" s="111"/>
       <c r="AL39" s="112"/>
-      <c r="AM39" s="4"/>
-      <c r="AN39" s="4"/>
-      <c r="AO39" s="4"/>
-      <c r="AP39" s="4"/>
-      <c r="AQ39" s="4"/>
-    </row>
-    <row r="40" spans="1:43" s="282" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:43" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="222"/>
       <c r="B40" s="216"/>
       <c r="C40" s="215"/>
@@ -7500,7 +7311,7 @@
       <c r="AP40" s="4"/>
       <c r="AQ40" s="4"/>
     </row>
-    <row r="41" spans="1:43" s="282" customFormat="1" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" customFormat="1" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A41" s="212" t="s">
         <v>49</v>
       </c>
@@ -7568,13 +7379,8 @@
       <c r="AJ41" s="111"/>
       <c r="AK41" s="111"/>
       <c r="AL41" s="112"/>
-      <c r="AM41"/>
-      <c r="AN41"/>
-      <c r="AO41"/>
-      <c r="AP41"/>
-      <c r="AQ41"/>
-    </row>
-    <row r="42" spans="1:43" s="282" customFormat="1" ht="112.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:43" customFormat="1" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A42" s="212"/>
       <c r="B42" s="214"/>
       <c r="C42" s="225"/>
@@ -7636,13 +7442,8 @@
       <c r="AJ42" s="111"/>
       <c r="AK42" s="111"/>
       <c r="AL42" s="112"/>
-      <c r="AM42"/>
-      <c r="AN42"/>
-      <c r="AO42"/>
-      <c r="AP42"/>
-      <c r="AQ42"/>
-    </row>
-    <row r="43" spans="1:43" s="282" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:43" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="221" t="s">
         <v>21</v>
       </c>
@@ -7710,13 +7511,8 @@
       <c r="AJ43" s="111"/>
       <c r="AK43" s="111"/>
       <c r="AL43" s="112"/>
-      <c r="AM43"/>
-      <c r="AN43"/>
-      <c r="AO43"/>
-      <c r="AP43"/>
-      <c r="AQ43"/>
-    </row>
-    <row r="44" spans="1:43" s="282" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:43" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="221"/>
       <c r="B44" s="214"/>
       <c r="C44" s="48" t="s">
@@ -7780,13 +7576,8 @@
       <c r="AJ44" s="111"/>
       <c r="AK44" s="111"/>
       <c r="AL44" s="112"/>
-      <c r="AM44"/>
-      <c r="AN44"/>
-      <c r="AO44"/>
-      <c r="AP44"/>
-      <c r="AQ44"/>
-    </row>
-    <row r="45" spans="1:43" s="282" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:43" customFormat="1" ht="75" x14ac:dyDescent="0.3">
       <c r="A45" s="221"/>
       <c r="B45" s="214"/>
       <c r="C45" s="246" t="s">
@@ -7850,13 +7641,8 @@
       <c r="AJ45" s="111"/>
       <c r="AK45" s="111"/>
       <c r="AL45" s="112"/>
-      <c r="AM45"/>
-      <c r="AN45"/>
-      <c r="AO45"/>
-      <c r="AP45"/>
-      <c r="AQ45"/>
-    </row>
-    <row r="46" spans="1:43" s="282" customFormat="1" ht="119.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:43" customFormat="1" ht="119.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="221"/>
       <c r="B46" s="214"/>
       <c r="C46" s="246"/>
@@ -7918,13 +7704,8 @@
       <c r="AJ46" s="111"/>
       <c r="AK46" s="111"/>
       <c r="AL46" s="112"/>
-      <c r="AM46"/>
-      <c r="AN46"/>
-      <c r="AO46"/>
-      <c r="AP46"/>
-      <c r="AQ46"/>
-    </row>
-    <row r="47" spans="1:43" s="282" customFormat="1" ht="112.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:43" customFormat="1" ht="112.5" x14ac:dyDescent="0.3">
       <c r="A47" s="212">
         <v>153</v>
       </c>
@@ -7992,13 +7773,8 @@
       <c r="AJ47" s="111"/>
       <c r="AK47" s="111"/>
       <c r="AL47" s="112"/>
-      <c r="AM47"/>
-      <c r="AN47"/>
-      <c r="AO47"/>
-      <c r="AP47"/>
-      <c r="AQ47"/>
-    </row>
-    <row r="48" spans="1:43" s="279" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:43" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="212"/>
       <c r="B48" s="214"/>
       <c r="C48" s="246"/>
@@ -8066,7 +7842,7 @@
       <c r="AP48"/>
       <c r="AQ48"/>
     </row>
-    <row r="49" spans="1:43" s="285" customFormat="1" ht="375" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43" s="6" customFormat="1" ht="375" x14ac:dyDescent="0.25">
       <c r="A49" s="222" t="s">
         <v>167</v>
       </c>
@@ -8140,7 +7916,7 @@
       <c r="AP49" s="5"/>
       <c r="AQ49" s="5"/>
     </row>
-    <row r="50" spans="1:43" s="285" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="222"/>
       <c r="B50" s="241"/>
       <c r="C50" s="225" t="s">
@@ -8204,13 +7980,8 @@
       <c r="AJ50" s="111"/>
       <c r="AK50" s="111"/>
       <c r="AL50" s="112"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="6"/>
-      <c r="AO50" s="6"/>
-      <c r="AP50" s="6"/>
-      <c r="AQ50" s="6"/>
-    </row>
-    <row r="51" spans="1:43" s="279" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:43" s="5" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="222"/>
       <c r="B51" s="241"/>
       <c r="C51" s="225"/>
@@ -8278,7 +8049,7 @@
       <c r="AP51" s="6"/>
       <c r="AQ51" s="6"/>
     </row>
-    <row r="52" spans="1:43" s="285" customFormat="1" ht="174" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43" s="6" customFormat="1" ht="174" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="142" t="s">
         <v>51</v>
       </c>
@@ -8352,7 +8123,7 @@
       <c r="AP52" s="5"/>
       <c r="AQ52" s="5"/>
     </row>
-    <row r="53" spans="1:43" s="285" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43" s="6" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="222" t="s">
         <v>96</v>
       </c>
@@ -8426,7 +8197,7 @@
       <c r="AP53" s="5"/>
       <c r="AQ53" s="5"/>
     </row>
-    <row r="54" spans="1:43" s="285" customFormat="1" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43" s="6" customFormat="1" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="222"/>
       <c r="B54" s="216"/>
       <c r="C54" s="249"/>
@@ -8494,7 +8265,7 @@
       <c r="AP54" s="5"/>
       <c r="AQ54" s="5"/>
     </row>
-    <row r="55" spans="1:43" s="285" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43" s="6" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="222"/>
       <c r="B55" s="216"/>
       <c r="C55" s="22" t="s">
@@ -8564,7 +8335,7 @@
       <c r="AP55" s="5"/>
       <c r="AQ55" s="5"/>
     </row>
-    <row r="56" spans="1:43" s="285" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="222"/>
       <c r="B56" s="216"/>
       <c r="C56" s="22" t="s">
@@ -8634,7 +8405,7 @@
       <c r="AP56" s="5"/>
       <c r="AQ56" s="5"/>
     </row>
-    <row r="57" spans="1:43" s="285" customFormat="1" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43" s="6" customFormat="1" ht="131.25" x14ac:dyDescent="0.25">
       <c r="A57" s="222"/>
       <c r="B57" s="216"/>
       <c r="C57" s="22" t="s">
@@ -8704,7 +8475,7 @@
       <c r="AP57" s="5"/>
       <c r="AQ57" s="5"/>
     </row>
-    <row r="58" spans="1:43" s="285" customFormat="1" ht="276.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43" s="6" customFormat="1" ht="276.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="222"/>
       <c r="B58" s="216"/>
       <c r="C58" s="22" t="s">
@@ -8794,7 +8565,7 @@
       <c r="AP58" s="5"/>
       <c r="AQ58" s="5"/>
     </row>
-    <row r="59" spans="1:43" s="286" customFormat="1" ht="206.25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:43" s="36" customFormat="1" ht="206.25" x14ac:dyDescent="0.3">
       <c r="A59" s="221" t="s">
         <v>168</v>
       </c>
@@ -8862,13 +8633,8 @@
       <c r="AJ59" s="111"/>
       <c r="AK59" s="111"/>
       <c r="AL59" s="112"/>
-      <c r="AM59" s="36"/>
-      <c r="AN59" s="36"/>
-      <c r="AO59" s="36"/>
-      <c r="AP59" s="36"/>
-      <c r="AQ59" s="36"/>
-    </row>
-    <row r="60" spans="1:43" s="286" customFormat="1" ht="131.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:43" s="36" customFormat="1" ht="131.25" x14ac:dyDescent="0.3">
       <c r="A60" s="221"/>
       <c r="B60" s="215"/>
       <c r="C60" s="213"/>
@@ -8923,13 +8689,8 @@
       <c r="AJ60" s="111"/>
       <c r="AK60" s="111"/>
       <c r="AL60" s="112"/>
-      <c r="AM60" s="36"/>
-      <c r="AN60" s="36"/>
-      <c r="AO60" s="36"/>
-      <c r="AP60" s="36"/>
-      <c r="AQ60" s="36"/>
-    </row>
-    <row r="61" spans="1:43" s="286" customFormat="1" ht="206.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:43" s="36" customFormat="1" ht="206.25" x14ac:dyDescent="0.3">
       <c r="A61" s="221"/>
       <c r="B61" s="215"/>
       <c r="C61" s="213" t="s">
@@ -8993,13 +8754,8 @@
       <c r="AJ61" s="111"/>
       <c r="AK61" s="111"/>
       <c r="AL61" s="112"/>
-      <c r="AM61" s="36"/>
-      <c r="AN61" s="36"/>
-      <c r="AO61" s="36"/>
-      <c r="AP61" s="36"/>
-      <c r="AQ61" s="36"/>
-    </row>
-    <row r="62" spans="1:43" s="286" customFormat="1" ht="150" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:43" s="36" customFormat="1" ht="150" x14ac:dyDescent="0.3">
       <c r="A62" s="221"/>
       <c r="B62" s="215"/>
       <c r="C62" s="213"/>
@@ -9054,13 +8810,8 @@
       <c r="AJ62" s="111"/>
       <c r="AK62" s="111"/>
       <c r="AL62" s="112"/>
-      <c r="AM62" s="36"/>
-      <c r="AN62" s="36"/>
-      <c r="AO62" s="36"/>
-      <c r="AP62" s="36"/>
-      <c r="AQ62" s="36"/>
-    </row>
-    <row r="63" spans="1:43" s="286" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:43" s="36" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="155" t="s">
         <v>360</v>
       </c>
@@ -9103,13 +8854,8 @@
       <c r="AJ63" s="111"/>
       <c r="AK63" s="111"/>
       <c r="AL63" s="112"/>
-      <c r="AM63" s="36"/>
-      <c r="AN63" s="36"/>
-      <c r="AO63" s="36"/>
-      <c r="AP63" s="36"/>
-      <c r="AQ63" s="36"/>
-    </row>
-    <row r="64" spans="1:43" s="286" customFormat="1" ht="243.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:43" s="36" customFormat="1" ht="243.75" x14ac:dyDescent="0.3">
       <c r="A64" s="219" t="s">
         <v>84</v>
       </c>
@@ -9177,13 +8923,8 @@
       <c r="AJ64" s="111"/>
       <c r="AK64" s="111"/>
       <c r="AL64" s="112"/>
-      <c r="AM64" s="36"/>
-      <c r="AN64" s="36"/>
-      <c r="AO64" s="36"/>
-      <c r="AP64" s="36"/>
-      <c r="AQ64" s="36"/>
-    </row>
-    <row r="65" spans="1:43" s="287" customFormat="1" ht="187.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:43" s="42" customFormat="1" ht="187.5" x14ac:dyDescent="0.3">
       <c r="A65" s="219"/>
       <c r="B65" s="220"/>
       <c r="C65" s="12" t="s">
@@ -9253,7 +8994,7 @@
       <c r="AP65" s="36"/>
       <c r="AQ65" s="36"/>
     </row>
-    <row r="66" spans="1:43" s="278" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:43" s="2" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="140" t="s">
         <v>70</v>
       </c>
@@ -9327,7 +9068,7 @@
       <c r="AP66" s="42"/>
       <c r="AQ66" s="42"/>
     </row>
-    <row r="67" spans="1:43" s="288" customFormat="1" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43" s="83" customFormat="1" ht="162" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="212" t="s">
         <v>71</v>
       </c>
@@ -9401,7 +9142,7 @@
       <c r="AP67" s="2"/>
       <c r="AQ67" s="2"/>
     </row>
-    <row r="68" spans="1:43" s="288" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43" s="83" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="212"/>
       <c r="B68" s="214"/>
       <c r="C68" s="102" t="s">
@@ -9465,13 +9206,8 @@
       <c r="AJ68" s="111"/>
       <c r="AK68" s="111"/>
       <c r="AL68" s="112"/>
-      <c r="AM68" s="83"/>
-      <c r="AN68" s="83"/>
-      <c r="AO68" s="83"/>
-      <c r="AP68" s="83"/>
-      <c r="AQ68" s="83"/>
-    </row>
-    <row r="69" spans="1:43" s="288" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:43" s="83" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="142" t="s">
         <v>313</v>
       </c>
@@ -9539,13 +9275,8 @@
       <c r="AJ69" s="111"/>
       <c r="AK69" s="111"/>
       <c r="AL69" s="112"/>
-      <c r="AM69" s="83"/>
-      <c r="AN69" s="83"/>
-      <c r="AO69" s="83"/>
-      <c r="AP69" s="83"/>
-      <c r="AQ69" s="83"/>
-    </row>
-    <row r="70" spans="1:43" s="288" customFormat="1" ht="198.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:43" s="83" customFormat="1" ht="198.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="142" t="s">
         <v>74</v>
       </c>
@@ -9613,13 +9344,8 @@
       <c r="AJ70" s="111"/>
       <c r="AK70" s="111"/>
       <c r="AL70" s="112"/>
-      <c r="AM70" s="83"/>
-      <c r="AN70" s="83"/>
-      <c r="AO70" s="83"/>
-      <c r="AP70" s="83"/>
-      <c r="AQ70" s="83"/>
-    </row>
-    <row r="71" spans="1:43" s="289" customFormat="1" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="71" spans="1:43" s="49" customFormat="1" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="235" t="s">
         <v>179</v>
       </c>
@@ -9644,29 +9370,8 @@
       <c r="T71" s="236"/>
       <c r="U71" s="236"/>
       <c r="V71" s="237"/>
-      <c r="W71" s="49"/>
-      <c r="X71" s="49"/>
-      <c r="Y71" s="49"/>
-      <c r="Z71" s="49"/>
-      <c r="AA71" s="49"/>
-      <c r="AB71" s="49"/>
-      <c r="AC71" s="49"/>
-      <c r="AD71" s="49"/>
-      <c r="AE71" s="49"/>
-      <c r="AF71" s="49"/>
-      <c r="AG71" s="49"/>
-      <c r="AH71" s="49"/>
-      <c r="AI71" s="49"/>
-      <c r="AJ71" s="49"/>
-      <c r="AK71" s="49"/>
-      <c r="AL71" s="49"/>
-      <c r="AM71" s="49"/>
-      <c r="AN71" s="49"/>
-      <c r="AO71" s="49"/>
-      <c r="AP71" s="49"/>
-      <c r="AQ71" s="49"/>
-    </row>
-    <row r="72" spans="1:43" s="289" customFormat="1" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="72" spans="1:43" s="49" customFormat="1" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="238"/>
       <c r="B72" s="239"/>
       <c r="C72" s="239"/>
@@ -9689,29 +9394,8 @@
       <c r="T72" s="239"/>
       <c r="U72" s="239"/>
       <c r="V72" s="240"/>
-      <c r="W72" s="49"/>
-      <c r="X72" s="49"/>
-      <c r="Y72" s="49"/>
-      <c r="Z72" s="49"/>
-      <c r="AA72" s="49"/>
-      <c r="AB72" s="49"/>
-      <c r="AC72" s="49"/>
-      <c r="AD72" s="49"/>
-      <c r="AE72" s="49"/>
-      <c r="AF72" s="49"/>
-      <c r="AG72" s="49"/>
-      <c r="AH72" s="49"/>
-      <c r="AI72" s="49"/>
-      <c r="AJ72" s="49"/>
-      <c r="AK72" s="49"/>
-      <c r="AL72" s="49"/>
-      <c r="AM72" s="49"/>
-      <c r="AN72" s="49"/>
-      <c r="AO72" s="49"/>
-      <c r="AP72" s="49"/>
-      <c r="AQ72" s="49"/>
-    </row>
-    <row r="73" spans="1:43" s="289" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="73" spans="1:43" s="49" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="226" t="s">
         <v>1</v>
       </c>
@@ -9738,29 +9422,8 @@
       <c r="T73" s="227"/>
       <c r="U73" s="227"/>
       <c r="V73" s="243"/>
-      <c r="W73" s="49"/>
-      <c r="X73" s="49"/>
-      <c r="Y73" s="49"/>
-      <c r="Z73" s="49"/>
-      <c r="AA73" s="49"/>
-      <c r="AB73" s="49"/>
-      <c r="AC73" s="49"/>
-      <c r="AD73" s="49"/>
-      <c r="AE73" s="49"/>
-      <c r="AF73" s="49"/>
-      <c r="AG73" s="49"/>
-      <c r="AH73" s="49"/>
-      <c r="AI73" s="49"/>
-      <c r="AJ73" s="49"/>
-      <c r="AK73" s="49"/>
-      <c r="AL73" s="49"/>
-      <c r="AM73" s="49"/>
-      <c r="AN73" s="49"/>
-      <c r="AO73" s="49"/>
-      <c r="AP73" s="49"/>
-      <c r="AQ73" s="49"/>
-    </row>
-    <row r="74" spans="1:43" s="289" customFormat="1" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="74" spans="1:43" s="49" customFormat="1" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="229"/>
       <c r="B74" s="230"/>
       <c r="C74" s="230"/>
@@ -9783,29 +9446,8 @@
       <c r="T74" s="230"/>
       <c r="U74" s="230"/>
       <c r="V74" s="245"/>
-      <c r="W74" s="49"/>
-      <c r="X74" s="49"/>
-      <c r="Y74" s="49"/>
-      <c r="Z74" s="49"/>
-      <c r="AA74" s="49"/>
-      <c r="AB74" s="49"/>
-      <c r="AC74" s="49"/>
-      <c r="AD74" s="49"/>
-      <c r="AE74" s="49"/>
-      <c r="AF74" s="49"/>
-      <c r="AG74" s="49"/>
-      <c r="AH74" s="49"/>
-      <c r="AI74" s="49"/>
-      <c r="AJ74" s="49"/>
-      <c r="AK74" s="49"/>
-      <c r="AL74" s="49"/>
-      <c r="AM74" s="49"/>
-      <c r="AN74" s="49"/>
-      <c r="AO74" s="49"/>
-      <c r="AP74" s="49"/>
-      <c r="AQ74" s="49"/>
-    </row>
-    <row r="75" spans="1:43" s="289" customFormat="1" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="75" spans="1:43" s="49" customFormat="1" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="50" t="s">
         <v>82</v>
       </c>
@@ -9830,27 +9472,6 @@
       <c r="T75" s="52"/>
       <c r="U75" s="52"/>
       <c r="V75" s="53"/>
-      <c r="W75" s="49"/>
-      <c r="X75" s="49"/>
-      <c r="Y75" s="49"/>
-      <c r="Z75" s="49"/>
-      <c r="AA75" s="49"/>
-      <c r="AB75" s="49"/>
-      <c r="AC75" s="49"/>
-      <c r="AD75" s="49"/>
-      <c r="AE75" s="49"/>
-      <c r="AF75" s="49"/>
-      <c r="AG75" s="49"/>
-      <c r="AH75" s="49"/>
-      <c r="AI75" s="49"/>
-      <c r="AJ75" s="49"/>
-      <c r="AK75" s="49"/>
-      <c r="AL75" s="49"/>
-      <c r="AM75" s="49"/>
-      <c r="AN75" s="49"/>
-      <c r="AO75" s="49"/>
-      <c r="AP75" s="49"/>
-      <c r="AQ75" s="49"/>
     </row>
     <row r="76" spans="1:43" ht="23.25" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A76" s="54" t="s">
@@ -14080,8 +13701,8 @@
     <mergeCell ref="C61:C62"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
-  <conditionalFormatting sqref="M10:M163">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="M9:M163">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="greaterThanOrEqual">
       <formula>$AQ$2</formula>
     </cfRule>
   </conditionalFormatting>
